--- a/testakten/hoai-leistungsphasen-kita-muehlenhof-lichtenrade-2026/04-lph3-entwurf-und-kostenberechnung.xlsx
+++ b/testakten/hoai-leistungsphasen-kita-muehlenhof-lichtenrade-2026/04-lph3-entwurf-und-kostenberechnung.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kostenberechnung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entscheidungen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budgetdrift" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anrechenbare_Kosten" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entscheidungen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,30 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F6F73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F3F1"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,12 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,52 +415,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kita Mühlenhof Kostenberechnung LPH 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Kita Muehlenhof - Kostenverfolgung ueber die Leistungsphasen (Betraege netto in EUR)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bezeichnung</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Kostenschätzung LPH2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Kostenberechnung LPH3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kostenschaetzung LPH 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kostenberechnung LPH 3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kostenanschlag LPH 7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Prognose/Ist LPH 8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Kommentar</t>
         </is>
@@ -494,7 +470,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bauwerk Baukonstruktion</t>
+          <t>Bauwerk - Baukonstruktion</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -504,11 +480,14 @@
         <v>2760000</v>
       </c>
       <c r="E4" t="n">
-        <v>310000</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Holzfassade und Gründung</t>
+        <v>2910000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2985000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Holzfassade und Gruendung; Nachtrag N-07 Baugrund</t>
         </is>
       </c>
     </row>
@@ -520,7 +499,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technische Anlagen</t>
+          <t>Bauwerk - Technische Anlagen</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -530,11 +509,14 @@
         <v>1190000</v>
       </c>
       <c r="E5" t="n">
-        <v>370000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Küche, Lüftung, PV, Sicherheitsbeleuchtung</t>
+        <v>1320000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vollkueche, Kuechenlueftung, PV, Sicherheitsbeleuchtung</t>
         </is>
       </c>
     </row>
@@ -546,7 +528,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Außenanlagen</t>
+          <t>Aussenanlagen und Freiflaechen</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -556,11 +538,14 @@
         <v>510000</v>
       </c>
       <c r="E6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spielgeräte und Entwässerung</t>
+        <v>545000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spielgeraete und Entwaesserung</t>
         </is>
       </c>
     </row>
@@ -582,18 +567,89 @@
         <v>770000</v>
       </c>
       <c r="E7" t="n">
-        <v>80000</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Planung/Prüfungen</t>
+        <v>805000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>835000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Planung, Pruefungen, Gutachten</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Summe Gesamtkosten</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4390000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5230000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5580000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5775000</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kostenobergrenze (Foerdermittelbescheid)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Politisch beschlossen zur Freigabe Variante B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ueber-/Unterschreitung Obergrenze</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>730000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Positiv = Ueberschreitung</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,98 +660,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kita Mühlenhof Kostenberechnung LPH 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Anrechenbare Kosten Gebaeude nach HOAI 2021 (KG 300 + KG 400)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Entscheidung</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Verantwortlich</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Leistungsstand</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KG 300</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KG 400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Anrechenbare Kosten</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Variante B fortführen</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Kostenobergrenze nicht angepasst</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bauherrin</t>
+          <t>Kostenschaetzung LPH 2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>820000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3270000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vorlaeufig</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Küche bleibt Vollküche</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Abluft/Brandschutz offen</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bauherrin/TGA</t>
+          <t>Kostenberechnung LPH 3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2760000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1190000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3950000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Massgeblich fuer das Honorar nach Paragraf 6 HOAI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Kostenanschlag LPH 7</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2910000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4230000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Erhoeht das Honorar nicht automatisch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Prognose/Ist LPH 8</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2985000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4380000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nur Kostenkontrolle, keine neue Honorarbasis</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Kostenrelevante Entscheidungen und offene Punkte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Entscheidung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Verantwortlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Variante B fortfuehren</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kostenobergrenze 4.500.000 EUR nicht angepasst</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bauherrin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kueche bleibt Vollkueche</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Abluftfuehrung und Brandschutz offen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bauherrin/TGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dachbegrünung plus PV</t>
+          <t>Dachbegruenung plus PV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -705,14 +886,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Architekt/TGA</t>
+          <t>Architektin/TGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nachtrag N-07 Baugrund angekuendigt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Schriftliche Anordnung fehlt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bauleitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kostenanschlag ueber Obergrenze</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Foerdermittelrechtlicher Nachweis erforderlich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bauherrin/Kanzlei</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>